--- a/raw/1970election.xlsx
+++ b/raw/1970election.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Dropbox/MyData/USvoting/historical voting/1920to1974/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4CEA77C-2FE0-2046-A1F5-23A703AFF586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05024215-5D0F-F844-8C77-D6B6A4B6D352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="14980" windowHeight="12340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6474" uniqueCount="1927">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6473" uniqueCount="1927">
   <si>
     <t>State</t>
   </si>
@@ -7636,7 +7636,7 @@
         <v>9</v>
       </c>
       <c r="G45">
-        <v>108358</v>
+        <v>62688</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -7659,7 +7659,7 @@
         <v>12</v>
       </c>
       <c r="G46">
-        <v>62688</v>
+        <v>108358</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -27482,8 +27482,8 @@
       <c r="C925" t="s">
         <v>7</v>
       </c>
-      <c r="D925" t="s">
-        <v>10</v>
+      <c r="D925">
+        <v>2</v>
       </c>
       <c r="E925" t="s">
         <v>1073</v>
